--- a/报表类型_知识包名称mapping.xlsx
+++ b/报表类型_知识包名称mapping.xlsx
@@ -38,7 +38,7 @@
     <t>customer type</t>
   </si>
   <si>
-    <t>客质月报_KPI字段定义文档.xlsx</t>
+    <t>客质月报_KPI字段定义文档_完整版.xlsx</t>
   </si>
 </sst>
 </file>
